--- a/data/Data_TK_mix.xlsx
+++ b/data/Data_TK_mix.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A12DD59-EC84-0D40-AED7-2D075E0F5634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF44CF5C-9415-A24F-BB3E-3F37F40A8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{C6B08C3F-F6AD-034E-B12B-418F659AF5D1}"/>
+    <workbookView xWindow="11560" yWindow="740" windowWidth="17840" windowHeight="18380" xr2:uid="{C6B08C3F-F6AD-034E-B12B-418F659AF5D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$N$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -634,6 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -692,7 +693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
@@ -739,7 +740,7 @@
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -785,7 +786,7 @@
         <v>125532</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
@@ -831,7 +832,7 @@
         <v>92474.9</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -877,7 +878,7 @@
         <v>112198</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
@@ -923,7 +924,7 @@
         <v>64413.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
@@ -969,7 +970,7 @@
         <v>67647.199999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
@@ -1015,7 +1016,7 @@
         <v>35850.300000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
@@ -1061,7 +1062,7 @@
         <v>36135.800000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>18</v>
       </c>
@@ -1107,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>18</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>127730.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>13</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
@@ -1294,7 +1295,7 @@
         <v>92474.9</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>13</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>112198</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>64413.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>13</v>
       </c>
@@ -1432,7 +1433,7 @@
         <v>67647.199999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>18</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>35850.300000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>13</v>
       </c>
@@ -1524,7 +1525,7 @@
         <v>36135.800000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
@@ -1570,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
@@ -1656,7 +1657,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>13</v>
       </c>
@@ -1696,7 +1697,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -1736,7 +1737,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>13</v>
       </c>
@@ -1776,7 +1777,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>18</v>
       </c>
@@ -1816,7 +1817,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>13</v>
       </c>
@@ -1856,7 +1857,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>18</v>
       </c>
@@ -1896,7 +1897,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>13</v>
       </c>
@@ -1936,7 +1937,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>18</v>
       </c>
@@ -1976,7 +1977,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>13</v>
       </c>
@@ -2016,7 +2017,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>18</v>
       </c>
@@ -2056,7 +2057,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
         <v>13</v>
       </c>
@@ -2097,7 +2098,7 @@
       <c r="N33" s="21"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>18</v>
       </c>
@@ -2137,7 +2138,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>13</v>
       </c>
@@ -2177,7 +2178,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>18</v>
       </c>
@@ -2217,7 +2218,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>13</v>
       </c>
@@ -2257,7 +2258,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>18</v>
       </c>
@@ -2297,7 +2298,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
         <v>13</v>
       </c>
@@ -2337,7 +2338,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>18</v>
       </c>
@@ -2377,7 +2378,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>13</v>
       </c>
@@ -2417,7 +2418,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2461,7 +2462,7 @@
         <v>2.7067911526064248</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>1.8524173027989819</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>1917.9899591746666</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>1713.6179056754597</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>1504.711601584607</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2681,7 +2682,7 @@
         <v>1800.3973546737802</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>1337.8252614824919</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>1609.1247894103492</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -2813,7 +2814,7 @@
         <v>1780.1710303503971</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>2343.2829840516674</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>12.123571101966164</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="19" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
         <v>13</v>
       </c>
@@ -2946,7 +2947,7 @@
       </c>
       <c r="O53"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -2990,7 +2991,7 @@
         <v>2136.6066770996345</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3034,7 +3035,7 @@
         <v>1672.8727133311424</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3078,7 +3079,7 @@
         <v>1321.5005540780139</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>1381.5796382086917</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -3166,7 +3167,7 @@
         <v>1120.9492424242426</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>2128.975588104749</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>1484.1783538274065</v>
       </c>
     </row>
-    <row r="61" spans="1:16" s="29" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" s="29" customFormat="1" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
         <v>13</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>1567.548163841808</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -3344,7 +3345,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -3436,7 +3437,7 @@
         <v>125532</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
         <v>18</v>
       </c>
@@ -3480,7 +3481,7 @@
         <v>6797.2</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
         <v>13</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>7021.3</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
         <v>18</v>
       </c>
@@ -3568,7 +3569,7 @@
         <v>5157.2</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="11" t="s">
         <v>13</v>
       </c>
@@ -3612,7 +3613,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
         <v>18</v>
       </c>
@@ -3656,7 +3657,7 @@
         <v>3519.5</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
         <v>13</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>3679.7</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
         <v>18</v>
       </c>
@@ -3744,7 +3745,7 @@
         <v>1418.2</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>13</v>
       </c>
@@ -3788,7 +3789,7 @@
         <v>2173.8000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="11" t="s">
         <v>18</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>13</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="11" t="s">
         <v>18</v>
       </c>
@@ -3920,7 +3921,7 @@
         <v>6797.2</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>13</v>
       </c>
@@ -3964,7 +3965,7 @@
         <v>7021.3</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
         <v>18</v>
       </c>
@@ -4008,7 +4009,7 @@
         <v>5157.2</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>13</v>
       </c>
@@ -4052,7 +4053,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="11" t="s">
         <v>18</v>
       </c>
@@ -4096,7 +4097,7 @@
         <v>3519.5</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>13</v>
       </c>
@@ -4140,7 +4141,7 @@
         <v>3679.7</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
         <v>18</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>1418.2</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="11" t="s">
         <v>13</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>2173.8000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
         <v>18</v>
       </c>
@@ -4316,7 +4317,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
         <v>18</v>
       </c>
@@ -4354,7 +4355,7 @@
         <v>725.8</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
         <v>13</v>
       </c>
@@ -4392,7 +4393,7 @@
         <v>942.6</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -4430,7 +4431,7 @@
         <v>642.70000000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>18</v>
       </c>
@@ -4468,7 +4469,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
         <v>13</v>
       </c>
@@ -4506,7 +4507,7 @@
         <v>604.5</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
         <v>18</v>
       </c>
@@ -4544,7 +4545,7 @@
         <v>814.7</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
         <v>13</v>
       </c>
@@ -4582,7 +4583,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>18</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>762.6</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
         <v>13</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>738.6</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
         <v>18</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>663.3</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
         <v>13</v>
       </c>
@@ -4734,7 +4735,7 @@
         <v>778.2</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
         <v>18</v>
       </c>
@@ -4772,7 +4773,7 @@
         <v>829.2</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
         <v>13</v>
       </c>
@@ -4810,7 +4811,7 @@
         <v>857.1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
         <v>18</v>
       </c>
@@ -4848,7 +4849,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
         <v>13</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>648.5</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
         <v>18</v>
       </c>
@@ -4924,7 +4925,7 @@
         <v>810.3</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="11" t="s">
         <v>13</v>
       </c>
@@ -4962,7 +4963,7 @@
         <v>716.2</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="11" t="s">
         <v>18</v>
       </c>
@@ -5000,7 +5001,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
         <v>13</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>576.1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="11" t="s">
         <v>18</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>630.4</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
         <v>13</v>
       </c>
@@ -5114,7 +5115,7 @@
         <v>691.8</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
         <v>18</v>
       </c>
@@ -5190,7 +5191,7 @@
         <v>642.20000000000005</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="11" t="s">
         <v>18</v>
       </c>
@@ -5234,7 +5235,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="11" t="s">
         <v>13</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
         <v>18</v>
       </c>
@@ -5366,7 +5367,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
         <v>13</v>
       </c>
@@ -5410,7 +5411,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="11" t="s">
         <v>18</v>
       </c>
@@ -5454,7 +5455,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
         <v>13</v>
       </c>
@@ -5498,7 +5499,7 @@
         <v>155.69999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
         <v>18</v>
       </c>
@@ -5542,7 +5543,7 @@
         <v>244.7</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
         <v>13</v>
       </c>
@@ -5583,7 +5584,7 @@
         <v>310.10000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
         <v>18</v>
       </c>
@@ -5627,7 +5628,7 @@
         <v>327.8</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="11" t="s">
         <v>13</v>
       </c>
@@ -5671,7 +5672,7 @@
         <v>541.1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
         <v>18</v>
       </c>
@@ -5715,7 +5716,7 @@
         <v>452.1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
         <v>13</v>
       </c>
@@ -5759,7 +5760,7 @@
         <v>558.1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
         <v>18</v>
       </c>
@@ -5803,7 +5804,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
         <v>13</v>
       </c>
@@ -5847,7 +5848,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="11" t="s">
         <v>18</v>
       </c>
@@ -5891,7 +5892,7 @@
         <v>159.80000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
         <v>13</v>
       </c>
@@ -5935,7 +5936,7 @@
         <v>155.69999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>18</v>
       </c>
@@ -5979,7 +5980,7 @@
         <v>330.5</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="11" t="s">
         <v>13</v>
       </c>
@@ -6020,7 +6021,7 @@
         <v>326.89999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
         <v>18</v>
       </c>
@@ -6064,7 +6065,7 @@
         <v>283.5</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
         <v>13</v>
       </c>
@@ -6108,7 +6109,7 @@
         <v>468.1</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="11" t="s">
         <v>18</v>
       </c>
@@ -6200,7 +6201,18 @@
       <c r="A131" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N61" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}"/>
+  <autoFilter ref="A1:N130" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="262"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="I"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Data_TK_mix.xlsx
+++ b/data/Data_TK_mix.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF44CF5C-9415-A24F-BB3E-3F37F40A8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8D7503-0EC3-634F-8043-8B7CBFE47B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11560" yWindow="740" windowWidth="17840" windowHeight="18380" xr2:uid="{C6B08C3F-F6AD-034E-B12B-418F659AF5D1}"/>
+    <workbookView xWindow="11560" yWindow="740" windowWidth="17840" windowHeight="18380" activeTab="1" xr2:uid="{C6B08C3F-F6AD-034E-B12B-418F659AF5D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$N$130</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="45">
   <si>
     <t>Ratio</t>
   </si>
@@ -111,6 +112,69 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>-   `Lot` : Two batches of earthworms were use and started at different times (D &amp; E).</t>
+  </si>
+  <si>
+    <t>-   `Date` : Date and hour of the measurement (DD-MM-YYY HH-MM format)</t>
+  </si>
+  <si>
+    <t>-   `t` : Number of days since the start of the experiment (range: 0-29).</t>
+  </si>
+  <si>
+    <t>-   `ID` : Identification number of the earthworm (range: 1-288).</t>
+  </si>
+  <si>
+    <t>-   `ID_cosm` : Identification number of the cosm (range: 1-143).</t>
+  </si>
+  <si>
+    <t>-   `Dose_EPX` : Nominal exposure concentration of epoxiconazole (mg/kg, range: 0-167).</t>
+  </si>
+  <si>
+    <t>-   `Dose_IMD` : Nominal exposure concentration of imidacloprid (mg/kg, range: 0-0.5).</t>
+  </si>
+  <si>
+    <t>-   `Ratio` : Toxic unit ratio between the two substances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   "E" : 100% Epoxiconazole &amp; 0% Imidacloprid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   "F" : 75% Epoxiconazole &amp; 25% Imidacloprid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   "G" : 50% Epoxiconazole &amp; 50% Imidacloprid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   "H" : 25% Epoxiconazole &amp; 75% Imidacloprid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   "I" : 0% Epoxiconazole &amp; 100% Imidacloprid.</t>
+  </si>
+  <si>
+    <t>-   `Line` : Identification number of the effect level (effect isobole under CA hypothesis) (range: 0-5)</t>
+  </si>
+  <si>
+    <t>-   `Nb_rep` : Replicate number (range: 1-3).</t>
+  </si>
+  <si>
+    <t>-   `No_vdt` : Identification number of the earthworm per replicate (range: 1-2).</t>
+  </si>
+  <si>
+    <t>-   `w` : Fresh weight of the earthworm (mg, range 296-1152).</t>
+  </si>
+  <si>
+    <t>-   `CiEPX` : Measured epoxiconazole concentration in the earthworm (ng/g, range: 22.4-95693).</t>
+  </si>
+  <si>
+    <t>-   `CiIMD` : Measured imidacloprid concentration in the earthworm (ng/g, range: 0.17-2343).</t>
+  </si>
+  <si>
+    <t>-   `CeEPX` : Measured epoxiconazole concentration in the soil (ng/g, range: 0-422).</t>
+  </si>
+  <si>
+    <t>-   `CeIMD` : Measured imidacloprid concentration in the soil (ng/g, range: 0-127730).</t>
   </si>
 </sst>
 </file>
@@ -634,7 +698,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -693,7 +756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
@@ -740,7 +803,7 @@
       </c>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -786,7 +849,7 @@
         <v>125532</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
@@ -832,7 +895,7 @@
         <v>92474.9</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -878,7 +941,7 @@
         <v>112198</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
@@ -924,7 +987,7 @@
         <v>64413.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
@@ -970,7 +1033,7 @@
         <v>67647.199999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
@@ -1016,7 +1079,7 @@
         <v>35850.300000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
@@ -1062,7 +1125,7 @@
         <v>36135.800000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>18</v>
       </c>
@@ -1108,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
@@ -1154,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>18</v>
       </c>
@@ -1200,7 +1263,7 @@
         <v>127730.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
@@ -1295,7 +1358,7 @@
         <v>92474.9</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>13</v>
       </c>
@@ -1341,7 +1404,7 @@
         <v>112198</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
@@ -1387,7 +1450,7 @@
         <v>64413.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>13</v>
       </c>
@@ -1433,7 +1496,7 @@
         <v>67647.199999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>18</v>
       </c>
@@ -1479,7 +1542,7 @@
         <v>35850.300000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>13</v>
       </c>
@@ -1525,7 +1588,7 @@
         <v>36135.800000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
@@ -1571,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
@@ -1617,7 +1680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
@@ -1657,7 +1720,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>13</v>
       </c>
@@ -1697,7 +1760,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -1737,7 +1800,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>13</v>
       </c>
@@ -1777,7 +1840,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>18</v>
       </c>
@@ -1817,7 +1880,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>13</v>
       </c>
@@ -1857,7 +1920,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>18</v>
       </c>
@@ -1897,7 +1960,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>13</v>
       </c>
@@ -1937,7 +2000,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>18</v>
       </c>
@@ -1977,7 +2040,7 @@
       <c r="M30" s="2"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>13</v>
       </c>
@@ -2017,7 +2080,7 @@
       <c r="M31" s="2"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>18</v>
       </c>
@@ -2057,7 +2120,7 @@
       <c r="M32" s="2"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:15" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
         <v>13</v>
       </c>
@@ -2098,7 +2161,7 @@
       <c r="N33" s="21"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>18</v>
       </c>
@@ -2138,7 +2201,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>13</v>
       </c>
@@ -2178,7 +2241,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>18</v>
       </c>
@@ -2218,7 +2281,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>13</v>
       </c>
@@ -2258,7 +2321,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>18</v>
       </c>
@@ -2298,7 +2361,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
         <v>13</v>
       </c>
@@ -2338,7 +2401,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>18</v>
       </c>
@@ -2378,7 +2441,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:15" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>13</v>
       </c>
@@ -2418,7 +2481,7 @@
       <c r="M41" s="15"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2462,7 +2525,7 @@
         <v>2.7067911526064248</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2506,7 +2569,7 @@
         <v>1.8524173027989819</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -2550,7 +2613,7 @@
         <v>1917.9899591746666</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2594,7 +2657,7 @@
         <v>1713.6179056754597</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2638,7 +2701,7 @@
         <v>1504.711601584607</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2682,7 +2745,7 @@
         <v>1800.3973546737802</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -2726,7 +2789,7 @@
         <v>1337.8252614824919</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -2770,7 +2833,7 @@
         <v>1609.1247894103492</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -2814,7 +2877,7 @@
         <v>1780.1710303503971</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -2858,7 +2921,7 @@
         <v>2343.2829840516674</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -2902,7 +2965,7 @@
         <v>12.123571101966164</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
         <v>13</v>
       </c>
@@ -2947,7 +3010,7 @@
       </c>
       <c r="O53"/>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -2991,7 +3054,7 @@
         <v>2136.6066770996345</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3035,7 +3098,7 @@
         <v>1672.8727133311424</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3079,7 +3142,7 @@
         <v>1321.5005540780139</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -3123,7 +3186,7 @@
         <v>1381.5796382086917</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -3167,7 +3230,7 @@
         <v>1120.9492424242426</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -3211,7 +3274,7 @@
         <v>2128.975588104749</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -3255,7 +3318,7 @@
         <v>1484.1783538274065</v>
       </c>
     </row>
-    <row r="61" spans="1:16" s="29" customFormat="1" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" s="29" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
         <v>13</v>
       </c>
@@ -3299,7 +3362,7 @@
         <v>1567.548163841808</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -3345,7 +3408,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3391,7 +3454,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -3437,7 +3500,7 @@
         <v>125532</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
         <v>18</v>
       </c>
@@ -3481,7 +3544,7 @@
         <v>6797.2</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
         <v>13</v>
       </c>
@@ -3525,7 +3588,7 @@
         <v>7021.3</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
         <v>18</v>
       </c>
@@ -3569,7 +3632,7 @@
         <v>5157.2</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="11" t="s">
         <v>13</v>
       </c>
@@ -3613,7 +3676,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
         <v>18</v>
       </c>
@@ -3657,7 +3720,7 @@
         <v>3519.5</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
         <v>13</v>
       </c>
@@ -3701,7 +3764,7 @@
         <v>3679.7</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
         <v>18</v>
       </c>
@@ -3745,7 +3808,7 @@
         <v>1418.2</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>13</v>
       </c>
@@ -3789,7 +3852,7 @@
         <v>2173.8000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" s="11" t="s">
         <v>18</v>
       </c>
@@ -3833,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>13</v>
       </c>
@@ -3877,7 +3940,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="11" t="s">
         <v>18</v>
       </c>
@@ -3921,7 +3984,7 @@
         <v>6797.2</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>13</v>
       </c>
@@ -3965,7 +4028,7 @@
         <v>7021.3</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
         <v>18</v>
       </c>
@@ -4009,7 +4072,7 @@
         <v>5157.2</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>13</v>
       </c>
@@ -4053,7 +4116,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="11" t="s">
         <v>18</v>
       </c>
@@ -4097,7 +4160,7 @@
         <v>3519.5</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>13</v>
       </c>
@@ -4141,7 +4204,7 @@
         <v>3679.7</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
         <v>18</v>
       </c>
@@ -4185,7 +4248,7 @@
         <v>1418.2</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" s="11" t="s">
         <v>13</v>
       </c>
@@ -4229,7 +4292,7 @@
         <v>2173.8000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
         <v>18</v>
       </c>
@@ -4317,7 +4380,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
         <v>18</v>
       </c>
@@ -4355,7 +4418,7 @@
         <v>725.8</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
         <v>13</v>
       </c>
@@ -4393,7 +4456,7 @@
         <v>942.6</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -4431,7 +4494,7 @@
         <v>642.70000000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>18</v>
       </c>
@@ -4469,7 +4532,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
         <v>13</v>
       </c>
@@ -4507,7 +4570,7 @@
         <v>604.5</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
         <v>18</v>
       </c>
@@ -4545,7 +4608,7 @@
         <v>814.7</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
         <v>13</v>
       </c>
@@ -4583,7 +4646,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>18</v>
       </c>
@@ -4621,7 +4684,7 @@
         <v>762.6</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
         <v>13</v>
       </c>
@@ -4659,7 +4722,7 @@
         <v>738.6</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
         <v>18</v>
       </c>
@@ -4697,7 +4760,7 @@
         <v>663.3</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
         <v>13</v>
       </c>
@@ -4735,7 +4798,7 @@
         <v>778.2</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
         <v>18</v>
       </c>
@@ -4773,7 +4836,7 @@
         <v>829.2</v>
       </c>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
         <v>13</v>
       </c>
@@ -4811,7 +4874,7 @@
         <v>857.1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
         <v>18</v>
       </c>
@@ -4849,7 +4912,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
         <v>13</v>
       </c>
@@ -4887,7 +4950,7 @@
         <v>648.5</v>
       </c>
     </row>
-    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
         <v>18</v>
       </c>
@@ -4925,7 +4988,7 @@
         <v>810.3</v>
       </c>
     </row>
-    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="11" t="s">
         <v>13</v>
       </c>
@@ -4963,7 +5026,7 @@
         <v>716.2</v>
       </c>
     </row>
-    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="11" t="s">
         <v>18</v>
       </c>
@@ -5001,7 +5064,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
         <v>13</v>
       </c>
@@ -5039,7 +5102,7 @@
         <v>576.1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="11" t="s">
         <v>18</v>
       </c>
@@ -5077,7 +5140,7 @@
         <v>630.4</v>
       </c>
     </row>
-    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
         <v>13</v>
       </c>
@@ -5115,7 +5178,7 @@
         <v>691.8</v>
       </c>
     </row>
-    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
         <v>18</v>
       </c>
@@ -5191,7 +5254,7 @@
         <v>642.20000000000005</v>
       </c>
     </row>
-    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="11" t="s">
         <v>18</v>
       </c>
@@ -5235,7 +5298,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="11" t="s">
         <v>13</v>
       </c>
@@ -5279,7 +5342,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -5323,7 +5386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
         <v>18</v>
       </c>
@@ -5367,7 +5430,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
         <v>13</v>
       </c>
@@ -5411,7 +5474,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="11" t="s">
         <v>18</v>
       </c>
@@ -5455,7 +5518,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
         <v>13</v>
       </c>
@@ -5499,7 +5562,7 @@
         <v>155.69999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
         <v>18</v>
       </c>
@@ -5543,7 +5606,7 @@
         <v>244.7</v>
       </c>
     </row>
-    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
         <v>13</v>
       </c>
@@ -5584,7 +5647,7 @@
         <v>310.10000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
         <v>18</v>
       </c>
@@ -5628,7 +5691,7 @@
         <v>327.8</v>
       </c>
     </row>
-    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="11" t="s">
         <v>13</v>
       </c>
@@ -5672,7 +5735,7 @@
         <v>541.1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
         <v>18</v>
       </c>
@@ -5716,7 +5779,7 @@
         <v>452.1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
         <v>13</v>
       </c>
@@ -5760,7 +5823,7 @@
         <v>558.1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
         <v>18</v>
       </c>
@@ -5804,7 +5867,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
         <v>13</v>
       </c>
@@ -5848,7 +5911,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="11" t="s">
         <v>18</v>
       </c>
@@ -5892,7 +5955,7 @@
         <v>159.80000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
         <v>13</v>
       </c>
@@ -5936,7 +5999,7 @@
         <v>155.69999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>18</v>
       </c>
@@ -5980,7 +6043,7 @@
         <v>330.5</v>
       </c>
     </row>
-    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="11" t="s">
         <v>13</v>
       </c>
@@ -6021,7 +6084,7 @@
         <v>326.89999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
         <v>18</v>
       </c>
@@ -6065,7 +6128,7 @@
         <v>283.5</v>
       </c>
     </row>
-    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
         <v>13</v>
       </c>
@@ -6109,7 +6172,7 @@
         <v>468.1</v>
       </c>
     </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="11" t="s">
         <v>18</v>
       </c>
@@ -6201,18 +6264,122 @@
       <c r="A131" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N130" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="262"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="I"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N130" xr:uid="{47352F90-BE75-B74B-9762-B8987616856A}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ADB0C8F-11D8-B74F-B8D0-E250BB1F9CEC}">
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>